--- a/demo_data/pnl.xlsx
+++ b/demo_data/pnl.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -450,7 +450,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1169.2779</v>
+        <v>463.5481</v>
       </c>
     </row>
     <row r="5">
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-311</v>
+        <v>-356</v>
       </c>
     </row>
     <row r="6">
@@ -470,7 +470,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-14699.1</v>
+        <v>-2040.57</v>
       </c>
     </row>
     <row r="7">
@@ -480,7 +480,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-72301.92999999999</v>
+        <v>39689.54</v>
       </c>
     </row>
     <row r="8">
@@ -519,7 +519,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>29.8449</v>
+        <v>11.9868</v>
       </c>
     </row>
     <row r="12">
@@ -529,7 +529,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5.571</v>
+        <v>2.2375</v>
       </c>
     </row>
     <row r="13">
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1004.8787</v>
+        <v>403.5956</v>
       </c>
     </row>
     <row r="14">
@@ -549,7 +549,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.0049</v>
+        <v>0.4036</v>
       </c>
     </row>
     <row r="15">
@@ -559,7 +559,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>127.8778</v>
+        <v>45.2842</v>
       </c>
     </row>
     <row r="16">
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1005</v>
+        <v>0.0404</v>
       </c>
     </row>
     <row r="17">
@@ -651,32 +651,32 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>25081.92</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>23838.72</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>-1243.2</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>446.82</v>
+        <v>540.5</v>
       </c>
       <c r="I18" t="n">
-        <v>317</v>
+        <v>0</v>
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="n">
-        <v>155080.29</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>-13438.96</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -694,32 +694,32 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>4</v>
+        <v>342</v>
       </c>
       <c r="D19" t="n">
-        <v>566.39</v>
+        <v>49508.29</v>
       </c>
       <c r="E19" t="n">
-        <v>573.84</v>
+        <v>49241.84</v>
       </c>
       <c r="F19" t="n">
-        <v>7.45</v>
+        <v>-266.45</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>99.40000000000001</v>
+        <v>145.98</v>
       </c>
       <c r="I19" t="n">
-        <v>1003</v>
+        <v>0</v>
       </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="n">
-        <v>142021.13</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>-42326.13</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -737,32 +737,32 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D20" t="n">
-        <v>6859.47</v>
+        <v>3394.57</v>
       </c>
       <c r="E20" t="n">
-        <v>6365.92</v>
+        <v>3582.35</v>
       </c>
       <c r="F20" t="n">
-        <v>-493.55</v>
+        <v>187.78</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>825.98</v>
+        <v>1074.79</v>
       </c>
       <c r="I20" t="n">
-        <v>159</v>
+        <v>56</v>
       </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="n">
-        <v>136331.99</v>
+        <v>47523.92</v>
       </c>
       <c r="L20" t="n">
-        <v>-5000.54</v>
+        <v>12664.49</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -780,22 +780,22 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2454</v>
+        <v>414</v>
       </c>
       <c r="D21" t="n">
-        <v>146333.91</v>
+        <v>25005.6</v>
       </c>
       <c r="E21" t="n">
-        <v>132810.48</v>
+        <v>24256.26</v>
       </c>
       <c r="F21" t="n">
-        <v>-13523.43</v>
+        <v>-749.34</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>53.14</v>
+        <v>44.63</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -814,41 +814,41 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>HEDWIG</t>
+          <t>DOBBY</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>INEHED01</t>
+          <t>INEDOB01</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>2699.95</v>
+        <v>230.74</v>
       </c>
       <c r="E22" t="n">
-        <v>2482.7</v>
+        <v>234.12</v>
       </c>
       <c r="F22" t="n">
-        <v>-217.25</v>
+        <v>3.38</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>230.27</v>
+        <v>274.32</v>
       </c>
       <c r="I22" t="n">
-        <v>523</v>
+        <v>219</v>
       </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="n">
-        <v>128370.33</v>
+        <v>50531.01</v>
       </c>
       <c r="L22" t="n">
-        <v>-7936.86</v>
+        <v>9545.58</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -857,43 +857,86 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>LUNA</t>
+          <t>ARAGOG</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>INELUN01</t>
+          <t>INEARA01</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>10599.12</v>
+        <v>520.27</v>
       </c>
       <c r="E23" t="n">
-        <v>10126.8</v>
+        <v>547.52</v>
       </c>
       <c r="F23" t="n">
-        <v>-472.32</v>
+        <v>27.25</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>428.77</v>
+        <v>631.8099999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>280</v>
+        <v>94</v>
       </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="n">
-        <v>123656.4</v>
+        <v>48905.14</v>
       </c>
       <c r="L23" t="n">
-        <v>-3599.44</v>
+        <v>10484.79</v>
       </c>
       <c r="M23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>BUCKBEAK</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>INEBUC01</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>108.56</v>
+      </c>
+      <c r="I24" t="n">
+        <v>536</v>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="n">
+        <v>51193.36</v>
+      </c>
+      <c r="L24" t="n">
+        <v>6994.68</v>
+      </c>
+      <c r="M24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -908,7 +951,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -973,12 +1016,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Being smallcase fee for 16/02/2026</t>
+          <t>Being smallcase fee for 10/03/2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -991,12 +1034,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DP Charges for Sale of DRACO on 04/03/2026</t>
+          <t>DP Charges for Sale of ALBUS on 05/03/2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1009,12 +1052,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DP Charges for Sale of CEDERY on 04/03/2026</t>
+          <t>DP Charges for Sale of ARAGOG on 09/04/2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1027,12 +1070,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DP Charges for Sale of CEDERY on 06/05/2026</t>
+          <t>DP Charges for Sale of BELLATRIX on 05/02/2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1045,12 +1088,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DP Charges for Sale of HEDWIG on 06/05/2026</t>
+          <t>DP Charges for Sale of BELLATRIX on 09/04/2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1063,18 +1106,72 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DP Charges for Sale of BELLATRIX on 04/03/2026</t>
+          <t>DP Charges for Sale of CEDERY on 05/03/2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>15</v>
       </c>
       <c r="D10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>DP Charges for Sale of CEDERY on 09/04/2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>15</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>DP Charges for Sale of DOBBY on 05/03/2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>15</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>DP Charges for Sale of DRACO on 05/02/2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>15</v>
+      </c>
+      <c r="D13" t="n">
         <v>0</v>
       </c>
     </row>

--- a/demo_data/pnl.xlsx
+++ b/demo_data/pnl.xlsx
@@ -728,7 +728,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CEDERY</t>
+          <t>CEDRIC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1106,7 +1106,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DP Charges for Sale of CEDERY on 05/03/2026</t>
+          <t>DP Charges for Sale of CEDRIC on 05/03/2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1124,7 +1124,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DP Charges for Sale of CEDERY on 09/04/2026</t>
+          <t>DP Charges for Sale of CEDRIC on 09/04/2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
